--- a/plantillas/29.xlsx
+++ b/plantillas/29.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="MARCA_1">Listas!$D$2:$D$2</definedName>
@@ -9320,7 +9320,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>24.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/29.xlsx
+++ b/plantillas/29.xlsx
@@ -9340,7 +9340,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>28.10.2026</t>
+          <t>29.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/29.xlsx
+++ b/plantillas/29.xlsx
@@ -9340,7 +9340,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>30.10.2026</t>
         </is>
       </c>
     </row>
